--- a/docs/design/03_詳細設計書_HackerLake.xlsx
+++ b/docs/design/03_詳細設計書_HackerLake.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phrx4\hackerlake\docs\design\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13AFF9CE-D41D-4CEE-91ED-FAE7A8B8B046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5E1DDAC-070B-4688-89E6-9473833E6BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{64DA517A-C473-44CD-96F7-CBE0489A781B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{8EA9EDCD-6256-41E1-ADD6-B5B493FFE879}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,18 @@
     <sheet name="ロジック設計" sheetId="4" r:id="rId4"/>
     <sheet name="安全設計" sheetId="5" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">コンポーネント設計!$A$3:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">ロジック設計!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">安全設計!$A$3:$H$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">状態管理!$A$3:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">表紙!$A$3:$H$6</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">コンポーネント設計!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">ロジック設計!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">安全設計!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">状態管理!$1:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">表紙!$1:$3</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -593,7 +605,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -620,15 +632,21 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
-      <name val="游ゴシック"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -644,6 +662,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF006080"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7FAFC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -677,7 +701,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -685,12 +709,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1006,18 +1033,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55609BE1-5398-4301-8718-7253A521A09E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48A9C9BA-BB10-4199-B366-BC2B1F739B8B}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1029,7 +1060,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1055,7 +1086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
@@ -1073,33 +1104,33 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5" s="5">
         <v>46186</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>20</v>
       </c>
@@ -1126,27 +1157,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H6" xr:uid="{48A9C9BA-BB10-4199-B366-BC2B1F739B8B}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD0E3D86-DA1F-4439-BEC2-CAC3B14EEC16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F85302B-6460-4B7E-87A0-3148A549768F}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>28</v>
       </c>
@@ -1158,7 +1195,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -1184,7 +1221,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>37</v>
       </c>
@@ -1210,33 +1247,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>52</v>
       </c>
@@ -1262,33 +1299,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>62</v>
       </c>
@@ -1314,54 +1351,60 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>44</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H9" xr:uid="{3F85302B-6460-4B7E-87A0-3148A549768F}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F646FC20-76C6-4F24-BA5C-0F7AA905BF90}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47948772-D86A-4121-B2FE-8D334105DD81}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>73</v>
       </c>
@@ -1373,7 +1416,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>74</v>
       </c>
@@ -1399,7 +1442,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>81</v>
       </c>
@@ -1425,33 +1468,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>95</v>
       </c>
@@ -1477,33 +1520,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>108</v>
       </c>
@@ -1529,33 +1572,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A9" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="H9" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>120</v>
       </c>
@@ -1582,27 +1625,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H10" xr:uid="{47948772-D86A-4121-B2FE-8D334105DD81}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A423E7F4-463F-4FCC-A80F-540A57BF9648}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40EC0610-EB56-421A-8BC5-3BAE011FC1AB}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>126</v>
       </c>
@@ -1614,7 +1663,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -1640,7 +1689,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>131</v>
       </c>
@@ -1666,33 +1715,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>143</v>
       </c>
@@ -1718,33 +1767,33 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A7" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="H7" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>156</v>
       </c>
@@ -1771,27 +1820,33 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H8" xr:uid="{40EC0610-EB56-421A-8BC5-3BAE011FC1AB}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C6EEC25-6EC1-4404-85B7-BE89EE6024C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13F08727-F16A-41DB-AADE-499546D7502D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="16.625" customWidth="1"/>
-    <col min="2" max="2" width="24.625" customWidth="1"/>
-    <col min="3" max="3" width="34.625" customWidth="1"/>
-    <col min="4" max="5" width="42.625" customWidth="1"/>
-    <col min="6" max="8" width="28.625" customWidth="1"/>
+    <col min="1" max="1" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="22.625" customWidth="1"/>
+    <col min="3" max="3" width="36.625" customWidth="1"/>
+    <col min="4" max="5" width="46.625" customWidth="1"/>
+    <col min="6" max="7" width="28.625" customWidth="1"/>
+    <col min="8" max="8" width="24.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>162</v>
       </c>
@@ -1803,7 +1858,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
     </row>
-    <row r="3" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="32.1" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>29</v>
       </c>
@@ -1829,7 +1884,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>169</v>
       </c>
@@ -1853,31 +1908,31 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:8" ht="33.950000000000003" customHeight="1">
+      <c r="A5" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" spans="1:8" ht="33.950000000000003" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>181</v>
       </c>
@@ -1902,10 +1957,12 @@
       <c r="H6" s="3"/>
     </row>
   </sheetData>
+  <autoFilter ref="A3:H6" xr:uid="{13F08727-F16A-41DB-AADE-499546D7502D}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.3" right="0.3" top="0.44999999999999996" bottom="0.44999999999999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="52" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>